--- a/cv5_cross_validation_metrics.xlsx
+++ b/cv5_cross_validation_metrics.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8978633003663262</v>
+        <v>0.900850592981811</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02685826378411692</v>
+        <v>0.01689698830020254</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7609145427286357</v>
+        <v>0.767736131934033</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03303334112035931</v>
+        <v>0.04352493488149718</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8961163522012578</v>
+        <v>0.9023899371069181</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008521425111455563</v>
+        <v>0.01603814819423052</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8409458884527604</v>
+        <v>0.8509363949565836</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01230091945225079</v>
+        <v>0.01798148287506336</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8388132491626139</v>
+        <v>0.8441680906812484</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01936447882539343</v>
+        <v>0.02373394057288714</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8394044795783927</v>
+        <v>0.8459420289855071</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01514446625286587</v>
+        <v>0.01487415260928499</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7986409256645046</v>
+        <v>0.8063433124749352</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02147575653965662</v>
+        <v>0.02299983148891273</v>
       </c>
     </row>
   </sheetData>
